--- a/res_ai/data/DS_Resume_Table/DS_Summ.xlsx
+++ b/res_ai/data/DS_Resume_Table/DS_Summ.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VaibhavNagar\Desktop\WAISL code's\qna_project\res_ai\data\DS_Resume_Table\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66C9EF8-1BA3-422A-BE7B-B308A846AD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Name</t>
   </si>
@@ -32,9 +26,6 @@
   </si>
   <si>
     <t>Divyansh's Resume (1).pdf</t>
-  </si>
-  <si>
-    <t>anil-yadav_resume.pdf</t>
   </si>
   <si>
     <t>The document provides information about Divyansh Khanna's experience as a Cyber Security Analyst at the Asian Institute of Technology in Thailand.
@@ -43,20 +34,46 @@
 Additionally, the document mentions their certifications, including 3SRC ACADEMY, G NOIDA, and Certified course of CYCBER SECURITY TECHNOLOGIES.</t>
   </si>
   <si>
+    <t>The candidate should have a B-Tech in Computer Science and Engineering with good Analytical Skills.</t>
+  </si>
+  <si>
+    <t>anil-yadav_resume.pdf</t>
+  </si>
+  <si>
     <t>The document provides a summary of the necessary skills required for the IT-Assistant Manager position at ANIL YADAV, including experience in IT Asset Management and Desktop Support, as well as experience in Remedy Force, Bomgar Remote Support, Azure AD, Manage Engine, SAP, Sophos Firewall, IT Asset Management Core Competencies, IT Operation, Incident Management, Service Request Management, Ticket Toll Management, SLA Management Profile Summary, Experience in Continuous Improvement, Work Experience, and IT Asset Management. The document provides information about the necessary skills required for a computer technician to be a Desktop, Laptop, and Server Support Engineer.
 The skills required include knowledge and experience of desktop environments and troubleshooting Windows 10, MAC OS related issues, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good understanding on infra technologies like SCCM, MS Intune, Desktop and Office 365, good</t>
   </si>
   <si>
-    <t>The candidate should have a B-Tech in Computer Science and Engineering with good Analytical Skills.</t>
-  </si>
-  <si>
     <t>The candidate should have a Master of Commerce degree from G.L.S College Banmore Morena, Jiwaji University, Gwalior Madhya Pradesh in 2014. The candidate should have a Microsoft Certified IT Certificate (MCP ID) and Foundation Certificate ID (GR671179055AY).</t>
+  </si>
+  <si>
+    <t>nikita-mahajan_resume.pdf</t>
+  </si>
+  <si>
+    <t>The document provides information on the necessary skills required to learn new skills and expand knowledge for an organization.
+It includes various courses such as Robotics, Python, SQL, TensorFlow &amp; Keras, NumPy &amp; Pandas, Machine Learning, Deep Learning, Tableau INTERESTS, Data Science, Data Analytics, Artificial Intelligence, Machine Learning, Deep Learning, Python, English Hindi Marathi, NIKITA MAHAJAN, Brain Tumor Detection using CNN and Transfer Learning, Object Detection with Yolo V3 using TensorFlow and Keras, Chat Bot, Breast Cancer Classification using Machine Learning, Customer Churn Prediction using Machine Learning, Diabetes Prediction using Machine Learning, and Azure Solutions and ChatGPT.
+The document also includes certification work experience, certification, and publications.</t>
+  </si>
+  <si>
+    <t>The candidate should have a Bachelor's degree in Electrical and Telecommunications from S.H.
+Mansukhani Institute of Technology, Ulhasnagar Mumbai University.</t>
+  </si>
+  <si>
+    <t>prateek-sachdeva_resume.pdf</t>
+  </si>
+  <si>
+    <t>The document provides information about Prateek Sachdeva's skills as a Data Analyst, Product Analyst, Data Quality Associate, Credit Risk, Data Extraction, Data Modeling, Scikit-Learn Pandas, Numpy Git, Data Visualisation, Power BI, Matplotlib MySQL, PostgreSQL, Deep Learning, Problem-Solving, Analytical Skills, Jupyter Notebook, Statistical Analysis, Predictive Analytics, Neural Networks, Achievements/Tasks, and Tasks. The document provides information about the skills required by the Analyst Victora Automotive, including Excel, Business Intelligence, Business Insights, Product Dashboard, Retail Sales Prediction, Book Recommender system, Singular Value Decomposition based Matrix Factorization, Singular Value Decomposition based Matrix Factorization, and Book Recommender system.
+The author also mentions their proficiency in English, Hindi, and Full Professional Proficiency.</t>
+  </si>
+  <si>
+    <t>The candidate should have a Bachelor's degree in Mechanical Engineering from Manav Rachna College of Engineering. The candidate should have a Full Stack Data Science Program qualification.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,10 +85,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,16 +108,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -109,40 +125,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="4">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -175,79 +191,79 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -268,54 +284,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -325,7 +340,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -334,7 +349,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -343,7 +358,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -351,10 +366,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -383,7 +398,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -396,13 +411,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -420,14 +434,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="138.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,26 +457,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="57">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="31.5">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="150" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="44.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="31.5">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
